--- a/archive/legacy_runs/lr_estimation_2025_07_21/est_lrs_by_category_filled.xlsx
+++ b/archive/legacy_runs/lr_estimation_2025_07_21/est_lrs_by_category_filled.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="n">
         <v>0.5</v>
@@ -485,13 +485,13 @@
         <v>0.4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +501,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
@@ -535,16 +535,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G4" t="n">
         <v>0.4</v>
@@ -553,7 +553,7 @@
         <v>1.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="5">
@@ -566,22 +566,22 @@
         <v>0.2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.2</v>
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.1</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.052</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -628,25 +628,25 @@
         <v>1.4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D7" t="n">
         <v>0.71</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H7" t="n">
         <v>0.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -656,25 +656,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G8" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
         <v>1.2</v>
@@ -687,25 +687,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="C9" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="F9" t="n">
         <v>0.4</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
       <c r="I9" t="n">
         <v>1.4</v>
@@ -721,17 +721,17 @@
         <v>1.2</v>
       </c>
       <c r="C10" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="E10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.3</v>
       </c>
-      <c r="F10" t="n">
-        <v>0.4</v>
-      </c>
       <c r="G10" t="n">
         <v>0.4</v>
       </c>
@@ -739,7 +739,7 @@
         <v>0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
         <v>0.2</v>
@@ -770,7 +770,7 @@
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E13" t="n">
         <v>0.2</v>
@@ -826,13 +826,13 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E14" t="n">
         <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G14" t="n">
         <v>0.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="15">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.1</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.3</v>
-      </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -907,25 +907,25 @@
         <v>2.5</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8</v>
+        <v>0.15</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="E17" t="n">
         <v>0.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="I17" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -975,16 +975,16 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I18" t="n">
         <v>0.4</v>
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="E19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="H19" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -1043,13 +1043,13 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1062,25 +1062,25 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.71</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.7</v>
-      </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G21" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H21" t="n">
         <v>1.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4</v>
+        <v>0.82</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>0.4</v>
@@ -1170,10 +1170,10 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.3</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G25" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="26">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="C26" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="E26" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="G26" t="n">
         <v>0.4</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="27">
@@ -1245,22 +1245,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C27" t="n">
         <v>1.8</v>
       </c>
       <c r="D27" t="n">
-        <v>0.866</v>
+        <v>0.7</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="H27" t="n">
         <v>0.8</v>
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="G28" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="29">
@@ -1307,25 +1307,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G29" t="n">
         <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.078</v>
+        <v>0.4</v>
       </c>
       <c r="I29" t="n">
         <v>1.4</v>
@@ -1338,28 +1338,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
         <v>0.2</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="31">
@@ -1369,25 +1369,25 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F31" t="n">
         <v>1.4</v>
       </c>
-      <c r="C31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>2.5</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.4</v>
-      </c>
       <c r="H31" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="I31" t="n">
         <v>1.2</v>
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2</v>
+        <v>0.53</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="H32" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.15</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="33">
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="C33" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="D33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H33" t="n">
         <v>0.7</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.3</v>
       </c>
       <c r="I33" t="n">
         <v>1.2</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.3</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H34" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="I34" t="n">
         <v>1.2</v>
@@ -1493,22 +1493,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="C35" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="D35" t="n">
         <v>0.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="F35" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H35" t="n">
         <v>0.4</v>
@@ -1524,28 +1524,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="C36" t="n">
         <v>2.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E36" t="n">
         <v>0.4</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="37">
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="38">
@@ -1586,28 +1586,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="C38" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E38" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F38" t="n">
         <v>0.75</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.39</v>
-      </c>
       <c r="G38" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="I38" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -1617,22 +1617,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G39" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>1.2</v>
@@ -1648,28 +1648,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E40" t="n">
         <v>0.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
@@ -1679,28 +1679,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F41" t="n">
         <v>0.71</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H41" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="42">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1725,13 +1725,13 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="I42" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43">
@@ -1741,28 +1741,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="G43" t="n">
         <v>0.71</v>
       </c>
       <c r="H43" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="44">
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C44" t="n">
-        <v>1.2</v>
+        <v>0.71</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -1790,10 +1790,10 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="45">
@@ -1803,28 +1803,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1849,13 +1849,13 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="47">
@@ -1865,28 +1865,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E47" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="F47" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="48">
@@ -1896,28 +1896,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
         <v>1.2</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="49">
@@ -1927,19 +1927,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="C49" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E49" t="n">
         <v>1.2</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G49" t="n">
         <v>1.2</v>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G50" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D51" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E51" t="n">
         <v>0.8</v>
@@ -2007,7 +2007,7 @@
         <v>0.9</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0.8</v>
@@ -2023,25 +2023,25 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D52" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I52" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="53">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C53" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D53" t="n">
         <v>0.71</v>
@@ -2063,16 +2063,16 @@
         <v>0.8</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G53" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="H53" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="54">
@@ -2085,19 +2085,19 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D54" t="n">
         <v>1.3</v>
       </c>
-      <c r="D54" t="n">
-        <v>1.4</v>
-      </c>
       <c r="E54" t="n">
         <v>0.8</v>
       </c>
       <c r="F54" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="G54" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
@@ -2113,28 +2113,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="D55" t="n">
         <v>0.5</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H55" t="n">
-        <v>1.04</v>
+        <v>0.71</v>
       </c>
       <c r="I55" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="56">
@@ -2144,19 +2144,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0.52</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F56" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0.8</v>
@@ -2165,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0.583</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="57">
@@ -2181,22 +2181,22 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E57" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G57" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.75</v>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1</v>
-      </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="59">
@@ -2240,25 +2240,25 @@
         <v>0.8</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="D59" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="60">
@@ -2268,28 +2268,28 @@
         </is>
       </c>
       <c r="B60" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.7</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="61">
@@ -2305,16 +2305,16 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="E61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G61" t="n">
         <v>0.7</v>
-      </c>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.8</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -2339,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -2348,10 +2348,10 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="63">
@@ -2367,16 +2367,16 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H63" t="n">
         <v>0.4</v>
@@ -2392,28 +2392,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="H64" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="65">
@@ -2423,28 +2423,28 @@
         </is>
       </c>
       <c r="B65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C65" t="n">
         <v>0.9</v>
       </c>
-      <c r="C65" t="n">
-        <v>0.4</v>
-      </c>
       <c r="D65" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G65" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H65" t="n">
         <v>1.4</v>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="66">
@@ -2463,19 +2463,19 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2485,28 +2485,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="68">
@@ -2519,25 +2519,25 @@
         <v>0.5</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E68" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="69">
@@ -2550,25 +2550,25 @@
         <v>0.8</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H69" t="n">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="70">
@@ -2584,10 +2584,10 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="E70" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="F70" t="n">
         <v>1</v>
@@ -2596,10 +2596,10 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="71">
@@ -2609,25 +2609,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="C71" t="n">
-        <v>0.22</v>
+        <v>0.71</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E71" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="F71" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="G71" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="H71" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="I71" t="n">
         <v>0.4</v>
@@ -2640,28 +2640,28 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E72" t="n">
         <v>0.3</v>
       </c>
-      <c r="C72" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.5</v>
-      </c>
       <c r="F72" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G72" t="n">
         <v>0.4</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="73">
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="C73" t="n">
         <v>0.4</v>
       </c>
       <c r="D73" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G73" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="H73" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="74">
@@ -2702,28 +2702,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D74" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="G74" t="n">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
       <c r="H74" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I74" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="75">
@@ -2736,25 +2736,25 @@
         <v>0.2</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="76">
@@ -2770,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>0.8</v>
@@ -2779,13 +2779,13 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="77">
@@ -2795,28 +2795,28 @@
         </is>
       </c>
       <c r="B77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I77" t="n">
         <v>0.7</v>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="78">
@@ -2826,28 +2826,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.47</v>
+        <v>0.8</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E78" t="n">
         <v>0.7</v>
       </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="79">
@@ -2860,10 +2860,10 @@
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E79" t="n">
         <v>0.8</v>
@@ -2875,10 +2875,10 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I79" t="n">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="80">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4</v>
+        <v>0.174</v>
       </c>
       <c r="C80" t="n">
-        <v>0.502</v>
+        <v>0.2</v>
       </c>
       <c r="D80" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I80" t="n">
         <v>1.4</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I80" t="n">
-        <v>1.1</v>
       </c>
     </row>
     <row r="81">
@@ -2919,28 +2919,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E81" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F81" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H81" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I81" t="n">
-        <v>0.71</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="82">
@@ -2950,16 +2950,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.2</v>
+        <v>0.71</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="E82" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
@@ -2968,10 +2968,10 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="83">
@@ -2987,10 +2987,10 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -3002,7 +3002,7 @@
         <v>0.2</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="84">
@@ -3012,28 +3012,28 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E84" t="n">
         <v>0.4</v>
       </c>
       <c r="F84" t="n">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="H84" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I84" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -3043,19 +3043,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0.253</v>
+        <v>0.4</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>0.4</v>
       </c>
       <c r="I85" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="86">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -3086,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G86" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
@@ -3120,13 +3120,13 @@
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8100000000000001</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0.49</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="88">
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D88" t="n">
         <v>0.8</v>
@@ -3148,16 +3148,16 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H88" t="n">
         <v>0.71</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H88" t="n">
-        <v>1</v>
-      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
